--- a/output/第10期計画素案_修正指示書_令和8年8月.xlsx
+++ b/output/第10期計画素案_修正指示書_令和8年8月.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>「算定不可」としていた4項目を代理指標に振り替え、指標名・データ源・基準値・目標を差し替えた。H07は3.4％、H08は8.7％、H12は20.4％、H16は給付実績により第10期に算定する。</t>
+          <t>「算定不可」としていた4項目を代理指標に振り替え、指標名・データ源・基準値・目標を差し替えた。H07は3.4％、H08は8.7％、H12は20.2％、H16は給付実績により第10期に算定する。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>20.4％（98票中20票）</t>
+          <t>20.2％（99票中20票）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>H12は在宅生活改善調査から20.4％として算定できる。H16は業務継続計画未策定減算の算定状況から算定できる。事業所を対象とする調査の実施は不要となる。</t>
+          <t>H12は在宅生活改善調査から20.2％として算定できる。H16は業務継続計画未策定減算の算定状況から算定できる。事業所を対象とする調査の実施は不要となる。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
